--- a/input/DAS_Validation_Thresholds.xlsx
+++ b/input/DAS_Validation_Thresholds.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -69,6 +69,9 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -127,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -171,6 +174,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -651,7 +660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2126,6 +2135,3696 @@
         <v>226</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="K18" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="L18" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="M18" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q18" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="S18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U18" s="17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V18" s="17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z18" s="17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="K19" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>111</v>
+      </c>
+      <c r="M19" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P19" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q19" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R19" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="S19" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="W19" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="X19" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y19" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z19" s="17" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>87</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="K20" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>149</v>
+      </c>
+      <c r="M20" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q20" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="R20" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="S20" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="U20" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="V20" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="W20" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="X20" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y20" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z20" s="17" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>134</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>81</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>154</v>
+      </c>
+      <c r="K21" s="17" t="n">
+        <v>128</v>
+      </c>
+      <c r="L21" s="17" t="n">
+        <v>207</v>
+      </c>
+      <c r="M21" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O21" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="P21" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q21" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="R21" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="S21" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T21" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="U21" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="V21" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="W21" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="X21" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y21" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z21" s="17" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>162</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>182</v>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v>160</v>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>207</v>
+      </c>
+      <c r="M22" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O22" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="P22" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q22" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="R22" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="S22" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="U22" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="V22" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="W22" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="X22" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="Y22" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z22" s="17" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>228</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>131</v>
+      </c>
+      <c r="J23" s="17" t="n">
+        <v>248</v>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v>190</v>
+      </c>
+      <c r="L23" s="17" t="n">
+        <v>325</v>
+      </c>
+      <c r="M23" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O23" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P23" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q23" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="R23" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="S23" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T23" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="U23" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="V23" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="W23" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="X23" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y23" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z23" s="17" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>277</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>157</v>
+      </c>
+      <c r="J24" s="17" t="n">
+        <v>297</v>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v>223</v>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>397</v>
+      </c>
+      <c r="M24" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O24" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="P24" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q24" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="R24" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="S24" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="T24" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="U24" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="V24" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="W24" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="X24" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y24" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z24" s="17" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>324</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>181</v>
+      </c>
+      <c r="J25" s="17" t="n">
+        <v>344</v>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v>253</v>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>445</v>
+      </c>
+      <c r="M25" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O25" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="P25" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q25" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="R25" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="S25" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="U25" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="V25" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="W25" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="X25" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="Y25" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z25" s="17" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>196</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>372</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>207</v>
+      </c>
+      <c r="J26" s="17" t="n">
+        <v>392</v>
+      </c>
+      <c r="K26" s="17" t="n">
+        <v>285</v>
+      </c>
+      <c r="L26" s="17" t="n">
+        <v>505</v>
+      </c>
+      <c r="M26" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="P26" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q26" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="R26" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="S26" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="T26" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="U26" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="V26" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="W26" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="X26" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y26" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z26" s="17" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>221</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>419</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>232</v>
+      </c>
+      <c r="J27" s="17" t="n">
+        <v>439</v>
+      </c>
+      <c r="K27" s="17" t="n">
+        <v>317</v>
+      </c>
+      <c r="L27" s="17" t="n">
+        <v>556</v>
+      </c>
+      <c r="M27" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="P27" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q27" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="R27" s="17" t="n">
+        <v>101</v>
+      </c>
+      <c r="S27" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T27" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="U27" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="V27" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="W27" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="X27" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y27" s="17" t="n">
+        <v>87</v>
+      </c>
+      <c r="Z27" s="17" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>248</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>467</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>259</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>487</v>
+      </c>
+      <c r="K28" s="17" t="n">
+        <v>348</v>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>624</v>
+      </c>
+      <c r="M28" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O28" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="P28" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q28" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="R28" s="17" t="n">
+        <v>112</v>
+      </c>
+      <c r="S28" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="T28" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="U28" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="V28" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="W28" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="X28" s="17" t="n">
+        <v>88</v>
+      </c>
+      <c r="Y28" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="Z28" s="17" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>342</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>659</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>353</v>
+      </c>
+      <c r="J29" s="17" t="n">
+        <v>679</v>
+      </c>
+      <c r="K29" s="17" t="n">
+        <v>466</v>
+      </c>
+      <c r="L29" s="17" t="n">
+        <v>851</v>
+      </c>
+      <c r="M29" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O29" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="P29" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q29" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="R29" s="17" t="n">
+        <v>151</v>
+      </c>
+      <c r="S29" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="T29" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="U29" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="V29" s="17" t="n">
+        <v>86</v>
+      </c>
+      <c r="W29" s="17" t="n">
+        <v>97</v>
+      </c>
+      <c r="X29" s="17" t="n">
+        <v>121</v>
+      </c>
+      <c r="Y29" s="17" t="n">
+        <v>132</v>
+      </c>
+      <c r="Z29" s="17" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>382</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>745</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>393</v>
+      </c>
+      <c r="J30" s="17" t="n">
+        <v>765</v>
+      </c>
+      <c r="K30" s="17" t="n">
+        <v>531</v>
+      </c>
+      <c r="L30" s="17" t="n">
+        <v>971</v>
+      </c>
+      <c r="M30" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O30" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="P30" s="17" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q30" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="R30" s="17" t="n">
+        <v>181</v>
+      </c>
+      <c r="S30" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="T30" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="U30" s="17" t="n">
+        <v>88</v>
+      </c>
+      <c r="V30" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="W30" s="17" t="n">
+        <v>113</v>
+      </c>
+      <c r="X30" s="17" t="n">
+        <v>138</v>
+      </c>
+      <c r="Y30" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="Z30" s="17" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>442</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>839</v>
+      </c>
+      <c r="I31" s="17" t="n">
+        <v>453</v>
+      </c>
+      <c r="J31" s="17" t="n">
+        <v>859</v>
+      </c>
+      <c r="K31" s="17" t="n">
+        <v>593</v>
+      </c>
+      <c r="L31" s="17" t="n">
+        <v>1089</v>
+      </c>
+      <c r="M31" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O31" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="P31" s="17" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q31" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="R31" s="17" t="n">
+        <v>196</v>
+      </c>
+      <c r="S31" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="T31" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="U31" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="V31" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="W31" s="17" t="n">
+        <v>126</v>
+      </c>
+      <c r="X31" s="17" t="n">
+        <v>155</v>
+      </c>
+      <c r="Y31" s="17" t="n">
+        <v>169</v>
+      </c>
+      <c r="Z31" s="17" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>588</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>1306</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>599</v>
+      </c>
+      <c r="J32" s="17" t="n">
+        <v>1326</v>
+      </c>
+      <c r="K32" s="17" t="n">
+        <v>624</v>
+      </c>
+      <c r="L32" s="17" t="n">
+        <v>1149</v>
+      </c>
+      <c r="M32" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N32" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O32" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="P32" s="17" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q32" s="17" t="n">
+        <v>66</v>
+      </c>
+      <c r="R32" s="17" t="n">
+        <v>207</v>
+      </c>
+      <c r="S32" s="17" t="n">
+        <v>66</v>
+      </c>
+      <c r="T32" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="U32" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="V32" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="W32" s="17" t="n">
+        <v>126</v>
+      </c>
+      <c r="X32" s="17" t="n">
+        <v>155</v>
+      </c>
+      <c r="Y32" s="17" t="n">
+        <v>169</v>
+      </c>
+      <c r="Z32" s="17" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F33" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="I33" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="J33" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="K33" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="L33" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="M33" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N33" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O33" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R33" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="S33" s="17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T33" s="17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U33" s="17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V33" s="17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W33" s="17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X33" s="17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y33" s="17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z33" s="17" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="J34" s="17" t="n">
+        <v>106</v>
+      </c>
+      <c r="K34" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="L34" s="17" t="n">
+        <v>111</v>
+      </c>
+      <c r="M34" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N34" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O34" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q34" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="R34" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="S34" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="T34" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="U34" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="V34" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="W34" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="X34" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y34" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z34" s="17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>87</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>128</v>
+      </c>
+      <c r="K35" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="L35" s="17" t="n">
+        <v>149</v>
+      </c>
+      <c r="M35" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O35" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="P35" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="R35" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="S35" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T35" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="U35" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="V35" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="W35" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="X35" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y35" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z35" s="17" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>134</v>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="J36" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="K36" s="17" t="n">
+        <v>128</v>
+      </c>
+      <c r="L36" s="17" t="n">
+        <v>207</v>
+      </c>
+      <c r="M36" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N36" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O36" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="P36" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q36" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="R36" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="S36" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="U36" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V36" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="W36" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="X36" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y36" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z36" s="17" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>162</v>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>118</v>
+      </c>
+      <c r="J37" s="17" t="n">
+        <v>203</v>
+      </c>
+      <c r="K37" s="17" t="n">
+        <v>160</v>
+      </c>
+      <c r="L37" s="17" t="n">
+        <v>207</v>
+      </c>
+      <c r="M37" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O37" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="P37" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q37" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="R37" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="S37" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T37" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="U37" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="V37" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="W37" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="X37" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y37" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z37" s="17" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>228</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>142</v>
+      </c>
+      <c r="J38" s="17" t="n">
+        <v>269</v>
+      </c>
+      <c r="K38" s="17" t="n">
+        <v>190</v>
+      </c>
+      <c r="L38" s="17" t="n">
+        <v>325</v>
+      </c>
+      <c r="M38" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O38" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P38" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q38" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="R38" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="S38" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="T38" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="U38" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="V38" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="W38" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="X38" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y38" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z38" s="17" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G39" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>277</v>
+      </c>
+      <c r="I39" s="17" t="n">
+        <v>168</v>
+      </c>
+      <c r="J39" s="17" t="n">
+        <v>318</v>
+      </c>
+      <c r="K39" s="17" t="n">
+        <v>223</v>
+      </c>
+      <c r="L39" s="17" t="n">
+        <v>397</v>
+      </c>
+      <c r="M39" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N39" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O39" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="P39" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q39" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="R39" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="S39" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="U39" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="V39" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="W39" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="X39" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y39" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z39" s="17" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>324</v>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>192</v>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>365</v>
+      </c>
+      <c r="K40" s="17" t="n">
+        <v>253</v>
+      </c>
+      <c r="L40" s="17" t="n">
+        <v>445</v>
+      </c>
+      <c r="M40" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N40" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O40" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="P40" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q40" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="R40" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="S40" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="T40" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="U40" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="V40" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="W40" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="X40" s="17" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y40" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="Z40" s="17" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D41" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F41" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G41" s="17" t="n">
+        <v>196</v>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>372</v>
+      </c>
+      <c r="I41" s="17" t="n">
+        <v>218</v>
+      </c>
+      <c r="J41" s="17" t="n">
+        <v>413</v>
+      </c>
+      <c r="K41" s="17" t="n">
+        <v>285</v>
+      </c>
+      <c r="L41" s="17" t="n">
+        <v>505</v>
+      </c>
+      <c r="M41" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O41" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="P41" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q41" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="R41" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="S41" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T41" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="U41" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="V41" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="W41" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="X41" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="Y41" s="17" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z41" s="17" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>221</v>
+      </c>
+      <c r="H42" s="17" t="n">
+        <v>419</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>243</v>
+      </c>
+      <c r="J42" s="17" t="n">
+        <v>460</v>
+      </c>
+      <c r="K42" s="17" t="n">
+        <v>317</v>
+      </c>
+      <c r="L42" s="17" t="n">
+        <v>556</v>
+      </c>
+      <c r="M42" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N42" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O42" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="P42" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q42" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="R42" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="S42" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="T42" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="U42" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="V42" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="W42" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="X42" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y42" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="Z42" s="17" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D43" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F43" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G43" s="17" t="n">
+        <v>248</v>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>467</v>
+      </c>
+      <c r="I43" s="17" t="n">
+        <v>270</v>
+      </c>
+      <c r="J43" s="17" t="n">
+        <v>508</v>
+      </c>
+      <c r="K43" s="17" t="n">
+        <v>348</v>
+      </c>
+      <c r="L43" s="17" t="n">
+        <v>624</v>
+      </c>
+      <c r="M43" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N43" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O43" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="P43" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q43" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="R43" s="17" t="n">
+        <v>118</v>
+      </c>
+      <c r="S43" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="T43" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="U43" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="V43" s="17" t="n">
+        <v>67</v>
+      </c>
+      <c r="W43" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="X43" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="Y43" s="17" t="n">
+        <v>102</v>
+      </c>
+      <c r="Z43" s="17" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G44" s="17" t="n">
+        <v>342</v>
+      </c>
+      <c r="H44" s="17" t="n">
+        <v>659</v>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>364</v>
+      </c>
+      <c r="J44" s="17" t="n">
+        <v>700</v>
+      </c>
+      <c r="K44" s="17" t="n">
+        <v>466</v>
+      </c>
+      <c r="L44" s="17" t="n">
+        <v>851</v>
+      </c>
+      <c r="M44" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N44" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O44" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="P44" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q44" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="R44" s="17" t="n">
+        <v>157</v>
+      </c>
+      <c r="S44" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="T44" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="U44" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="V44" s="17" t="n">
+        <v>91</v>
+      </c>
+      <c r="W44" s="17" t="n">
+        <v>102</v>
+      </c>
+      <c r="X44" s="17" t="n">
+        <v>126</v>
+      </c>
+      <c r="Y44" s="17" t="n">
+        <v>138</v>
+      </c>
+      <c r="Z44" s="17" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>382</v>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>745</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>404</v>
+      </c>
+      <c r="J45" s="17" t="n">
+        <v>786</v>
+      </c>
+      <c r="K45" s="17" t="n">
+        <v>531</v>
+      </c>
+      <c r="L45" s="17" t="n">
+        <v>971</v>
+      </c>
+      <c r="M45" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N45" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O45" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="P45" s="17" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q45" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="R45" s="17" t="n">
+        <v>187</v>
+      </c>
+      <c r="S45" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="T45" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="U45" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="V45" s="17" t="n">
+        <v>103</v>
+      </c>
+      <c r="W45" s="17" t="n">
+        <v>118</v>
+      </c>
+      <c r="X45" s="17" t="n">
+        <v>143</v>
+      </c>
+      <c r="Y45" s="17" t="n">
+        <v>156</v>
+      </c>
+      <c r="Z45" s="17" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F46" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>442</v>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>839</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>464</v>
+      </c>
+      <c r="J46" s="17" t="n">
+        <v>880</v>
+      </c>
+      <c r="K46" s="17" t="n">
+        <v>593</v>
+      </c>
+      <c r="L46" s="17" t="n">
+        <v>1089</v>
+      </c>
+      <c r="M46" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N46" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O46" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="P46" s="17" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q46" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="R46" s="17" t="n">
+        <v>202</v>
+      </c>
+      <c r="S46" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="T46" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="U46" s="17" t="n">
+        <v>103</v>
+      </c>
+      <c r="V46" s="17" t="n">
+        <v>115</v>
+      </c>
+      <c r="W46" s="17" t="n">
+        <v>131</v>
+      </c>
+      <c r="X46" s="17" t="n">
+        <v>160</v>
+      </c>
+      <c r="Y46" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="Z46" s="17" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>588</v>
+      </c>
+      <c r="H47" s="17" t="n">
+        <v>1306</v>
+      </c>
+      <c r="I47" s="17" t="n">
+        <v>610</v>
+      </c>
+      <c r="J47" s="17" t="n">
+        <v>1347</v>
+      </c>
+      <c r="K47" s="17" t="n">
+        <v>624</v>
+      </c>
+      <c r="L47" s="17" t="n">
+        <v>1149</v>
+      </c>
+      <c r="M47" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O47" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="P47" s="17" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q47" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="R47" s="17" t="n">
+        <v>213</v>
+      </c>
+      <c r="S47" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="T47" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="U47" s="17" t="n">
+        <v>103</v>
+      </c>
+      <c r="V47" s="17" t="n">
+        <v>115</v>
+      </c>
+      <c r="W47" s="17" t="n">
+        <v>131</v>
+      </c>
+      <c r="X47" s="17" t="n">
+        <v>160</v>
+      </c>
+      <c r="Y47" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="Z47" s="17" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="H48" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="I48" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="J48" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="K48" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="L48" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="M48" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N48" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="R48" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="S48" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V48" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="W48" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="X48" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z48" s="17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D49" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F49" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G49" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="J49" s="17" t="n">
+        <v>102</v>
+      </c>
+      <c r="K49" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="L49" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="M49" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N49" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O49" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P49" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q49" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="R49" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="S49" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T49" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U49" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="V49" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="W49" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="X49" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y49" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z49" s="17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="H50" s="17" t="n">
+        <v>87</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>148</v>
+      </c>
+      <c r="K50" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="L50" s="17" t="n">
+        <v>149</v>
+      </c>
+      <c r="M50" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N50" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O50" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="P50" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="R50" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="S50" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="T50" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="U50" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="V50" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="W50" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="X50" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y50" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z50" s="17" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G51" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="H51" s="17" t="n">
+        <v>134</v>
+      </c>
+      <c r="I51" s="17" t="n">
+        <v>103</v>
+      </c>
+      <c r="J51" s="17" t="n">
+        <v>195</v>
+      </c>
+      <c r="K51" s="17" t="n">
+        <v>128</v>
+      </c>
+      <c r="L51" s="17" t="n">
+        <v>207</v>
+      </c>
+      <c r="M51" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N51" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O51" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="P51" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q51" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="R51" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="S51" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T51" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="U51" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="V51" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="W51" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="X51" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y51" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z51" s="17" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G52" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="H52" s="17" t="n">
+        <v>162</v>
+      </c>
+      <c r="I52" s="17" t="n">
+        <v>129</v>
+      </c>
+      <c r="J52" s="17" t="n">
+        <v>223</v>
+      </c>
+      <c r="K52" s="17" t="n">
+        <v>160</v>
+      </c>
+      <c r="L52" s="17" t="n">
+        <v>207</v>
+      </c>
+      <c r="M52" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N52" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O52" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="P52" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q52" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="R52" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="S52" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="T52" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="U52" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="V52" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="W52" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="X52" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="Y52" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z52" s="17" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C53" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D53" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G53" s="17" t="n">
+        <v>120</v>
+      </c>
+      <c r="H53" s="17" t="n">
+        <v>228</v>
+      </c>
+      <c r="I53" s="17" t="n">
+        <v>153</v>
+      </c>
+      <c r="J53" s="17" t="n">
+        <v>289</v>
+      </c>
+      <c r="K53" s="17" t="n">
+        <v>190</v>
+      </c>
+      <c r="L53" s="17" t="n">
+        <v>325</v>
+      </c>
+      <c r="M53" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N53" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O53" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P53" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q53" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="R53" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="S53" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="U53" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="V53" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="W53" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="X53" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y53" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z53" s="17" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D54" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F54" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G54" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="H54" s="17" t="n">
+        <v>277</v>
+      </c>
+      <c r="I54" s="17" t="n">
+        <v>179</v>
+      </c>
+      <c r="J54" s="17" t="n">
+        <v>338</v>
+      </c>
+      <c r="K54" s="17" t="n">
+        <v>223</v>
+      </c>
+      <c r="L54" s="17" t="n">
+        <v>397</v>
+      </c>
+      <c r="M54" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N54" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O54" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="P54" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q54" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="R54" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="S54" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="T54" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="U54" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="V54" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="W54" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="X54" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y54" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z54" s="17" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="D55" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G55" s="17" t="n">
+        <v>170</v>
+      </c>
+      <c r="H55" s="17" t="n">
+        <v>324</v>
+      </c>
+      <c r="I55" s="17" t="n">
+        <v>203</v>
+      </c>
+      <c r="J55" s="17" t="n">
+        <v>385</v>
+      </c>
+      <c r="K55" s="17" t="n">
+        <v>253</v>
+      </c>
+      <c r="L55" s="17" t="n">
+        <v>445</v>
+      </c>
+      <c r="M55" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N55" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O55" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="P55" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q55" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="R55" s="17" t="n">
+        <v>91</v>
+      </c>
+      <c r="S55" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="T55" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="U55" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="V55" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="W55" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="X55" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="Y55" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z55" s="17" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C56" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D56" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G56" s="17" t="n">
+        <v>196</v>
+      </c>
+      <c r="H56" s="17" t="n">
+        <v>372</v>
+      </c>
+      <c r="I56" s="17" t="n">
+        <v>229</v>
+      </c>
+      <c r="J56" s="17" t="n">
+        <v>433</v>
+      </c>
+      <c r="K56" s="17" t="n">
+        <v>285</v>
+      </c>
+      <c r="L56" s="17" t="n">
+        <v>505</v>
+      </c>
+      <c r="M56" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N56" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O56" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="P56" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q56" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="R56" s="17" t="n">
+        <v>102</v>
+      </c>
+      <c r="S56" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="T56" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="U56" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="V56" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="W56" s="17" t="n">
+        <v>67</v>
+      </c>
+      <c r="X56" s="17" t="n">
+        <v>81</v>
+      </c>
+      <c r="Y56" s="17" t="n">
+        <v>89</v>
+      </c>
+      <c r="Z56" s="17" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C57" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D57" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F57" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G57" s="17" t="n">
+        <v>221</v>
+      </c>
+      <c r="H57" s="17" t="n">
+        <v>419</v>
+      </c>
+      <c r="I57" s="17" t="n">
+        <v>254</v>
+      </c>
+      <c r="J57" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="K57" s="17" t="n">
+        <v>317</v>
+      </c>
+      <c r="L57" s="17" t="n">
+        <v>556</v>
+      </c>
+      <c r="M57" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N57" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O57" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="P57" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q57" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="R57" s="17" t="n">
+        <v>113</v>
+      </c>
+      <c r="S57" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="T57" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="U57" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="V57" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="W57" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="X57" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y57" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="Z57" s="17" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C58" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D58" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G58" s="17" t="n">
+        <v>248</v>
+      </c>
+      <c r="H58" s="17" t="n">
+        <v>467</v>
+      </c>
+      <c r="I58" s="17" t="n">
+        <v>281</v>
+      </c>
+      <c r="J58" s="17" t="n">
+        <v>528</v>
+      </c>
+      <c r="K58" s="17" t="n">
+        <v>348</v>
+      </c>
+      <c r="L58" s="17" t="n">
+        <v>624</v>
+      </c>
+      <c r="M58" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N58" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O58" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="P58" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q58" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="R58" s="17" t="n">
+        <v>124</v>
+      </c>
+      <c r="S58" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="T58" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="U58" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="V58" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="W58" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="X58" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="Y58" s="17" t="n">
+        <v>108</v>
+      </c>
+      <c r="Z58" s="17" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C59" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D59" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F59" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G59" s="17" t="n">
+        <v>342</v>
+      </c>
+      <c r="H59" s="17" t="n">
+        <v>659</v>
+      </c>
+      <c r="I59" s="17" t="n">
+        <v>375</v>
+      </c>
+      <c r="J59" s="17" t="n">
+        <v>720</v>
+      </c>
+      <c r="K59" s="17" t="n">
+        <v>466</v>
+      </c>
+      <c r="L59" s="17" t="n">
+        <v>851</v>
+      </c>
+      <c r="M59" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N59" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O59" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="P59" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q59" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="R59" s="17" t="n">
+        <v>163</v>
+      </c>
+      <c r="S59" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="T59" s="17" t="n">
+        <v>67</v>
+      </c>
+      <c r="U59" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="V59" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="W59" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="X59" s="17" t="n">
+        <v>131</v>
+      </c>
+      <c r="Y59" s="17" t="n">
+        <v>144</v>
+      </c>
+      <c r="Z59" s="17" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C60" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D60" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G60" s="17" t="n">
+        <v>382</v>
+      </c>
+      <c r="H60" s="17" t="n">
+        <v>745</v>
+      </c>
+      <c r="I60" s="17" t="n">
+        <v>415</v>
+      </c>
+      <c r="J60" s="17" t="n">
+        <v>806</v>
+      </c>
+      <c r="K60" s="17" t="n">
+        <v>531</v>
+      </c>
+      <c r="L60" s="17" t="n">
+        <v>971</v>
+      </c>
+      <c r="M60" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N60" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O60" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="P60" s="17" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q60" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="R60" s="17" t="n">
+        <v>193</v>
+      </c>
+      <c r="S60" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="T60" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="U60" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="V60" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="W60" s="17" t="n">
+        <v>123</v>
+      </c>
+      <c r="X60" s="17" t="n">
+        <v>148</v>
+      </c>
+      <c r="Y60" s="17" t="n">
+        <v>162</v>
+      </c>
+      <c r="Z60" s="17" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C61" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D61" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F61" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G61" s="17" t="n">
+        <v>442</v>
+      </c>
+      <c r="H61" s="17" t="n">
+        <v>839</v>
+      </c>
+      <c r="I61" s="17" t="n">
+        <v>475</v>
+      </c>
+      <c r="J61" s="17" t="n">
+        <v>900</v>
+      </c>
+      <c r="K61" s="17" t="n">
+        <v>593</v>
+      </c>
+      <c r="L61" s="17" t="n">
+        <v>1089</v>
+      </c>
+      <c r="M61" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N61" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O61" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="P61" s="17" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q61" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="R61" s="17" t="n">
+        <v>208</v>
+      </c>
+      <c r="S61" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="T61" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="U61" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="V61" s="17" t="n">
+        <v>119</v>
+      </c>
+      <c r="W61" s="17" t="n">
+        <v>136</v>
+      </c>
+      <c r="X61" s="17" t="n">
+        <v>165</v>
+      </c>
+      <c r="Y61" s="17" t="n">
+        <v>181</v>
+      </c>
+      <c r="Z61" s="17" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>SISO</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C62" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D62" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="F62" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="G62" s="17" t="n">
+        <v>588</v>
+      </c>
+      <c r="H62" s="17" t="n">
+        <v>1306</v>
+      </c>
+      <c r="I62" s="17" t="n">
+        <v>621</v>
+      </c>
+      <c r="J62" s="17" t="n">
+        <v>1367</v>
+      </c>
+      <c r="K62" s="17" t="n">
+        <v>624</v>
+      </c>
+      <c r="L62" s="17" t="n">
+        <v>1149</v>
+      </c>
+      <c r="M62" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N62" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O62" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="P62" s="17" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q62" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="R62" s="17" t="n">
+        <v>219</v>
+      </c>
+      <c r="S62" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="T62" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="U62" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="V62" s="17" t="n">
+        <v>119</v>
+      </c>
+      <c r="W62" s="17" t="n">
+        <v>136</v>
+      </c>
+      <c r="X62" s="17" t="n">
+        <v>165</v>
+      </c>
+      <c r="Y62" s="17" t="n">
+        <v>181</v>
+      </c>
+      <c r="Z62" s="17" t="n">
+        <v>220</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2137,7 +5836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z17"/>
+  <dimension ref="A1:Z62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3612,6 +7311,3696 @@
         <v>226</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F18" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G18" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="H18" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="J18" s="17" t="n">
+        <v>121</v>
+      </c>
+      <c r="K18" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="L18" s="17" t="n">
+        <v>141</v>
+      </c>
+      <c r="M18" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N18" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q18" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="S18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U18" s="17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="V18" s="17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z18" s="17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G19" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="H19" s="17" t="n">
+        <v>130</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="J19" s="17" t="n">
+        <v>169</v>
+      </c>
+      <c r="K19" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="L19" s="17" t="n">
+        <v>223</v>
+      </c>
+      <c r="M19" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N19" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O19" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P19" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q19" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="R19" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="S19" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="V19" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="W19" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="X19" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y19" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z19" s="17" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C20" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G20" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="H20" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>113</v>
+      </c>
+      <c r="J20" s="17" t="n">
+        <v>214</v>
+      </c>
+      <c r="K20" s="17" t="n">
+        <v>195</v>
+      </c>
+      <c r="L20" s="17" t="n">
+        <v>298</v>
+      </c>
+      <c r="M20" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N20" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O20" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="P20" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q20" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="R20" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="S20" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="U20" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="V20" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="W20" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="X20" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y20" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z20" s="17" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F21" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <v>141</v>
+      </c>
+      <c r="H21" s="17" t="n">
+        <v>267</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>162</v>
+      </c>
+      <c r="J21" s="17" t="n">
+        <v>306</v>
+      </c>
+      <c r="K21" s="17" t="n">
+        <v>256</v>
+      </c>
+      <c r="L21" s="17" t="n">
+        <v>414</v>
+      </c>
+      <c r="M21" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N21" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O21" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="P21" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q21" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="R21" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="S21" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T21" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="U21" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="V21" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="W21" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="X21" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y21" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z21" s="17" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C22" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D22" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F22" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G22" s="17" t="n">
+        <v>191</v>
+      </c>
+      <c r="H22" s="17" t="n">
+        <v>363</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <v>212</v>
+      </c>
+      <c r="J22" s="17" t="n">
+        <v>402</v>
+      </c>
+      <c r="K22" s="17" t="n">
+        <v>330</v>
+      </c>
+      <c r="L22" s="17" t="n">
+        <v>534</v>
+      </c>
+      <c r="M22" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O22" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="P22" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q22" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="R22" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="S22" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="U22" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="V22" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="W22" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="X22" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="Y22" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z22" s="17" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F23" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G23" s="17" t="n">
+        <v>240</v>
+      </c>
+      <c r="H23" s="17" t="n">
+        <v>455</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>261</v>
+      </c>
+      <c r="J23" s="17" t="n">
+        <v>494</v>
+      </c>
+      <c r="K23" s="17" t="n">
+        <v>380</v>
+      </c>
+      <c r="L23" s="17" t="n">
+        <v>650</v>
+      </c>
+      <c r="M23" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O23" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P23" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q23" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="R23" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="S23" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="T23" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="U23" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="V23" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="W23" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="X23" s="17" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y23" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="Z23" s="17" t="n">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C24" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G24" s="17" t="n">
+        <v>292</v>
+      </c>
+      <c r="H24" s="17" t="n">
+        <v>555</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <v>313</v>
+      </c>
+      <c r="J24" s="17" t="n">
+        <v>594</v>
+      </c>
+      <c r="K24" s="17" t="n">
+        <v>446</v>
+      </c>
+      <c r="L24" s="17" t="n">
+        <v>774</v>
+      </c>
+      <c r="M24" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O24" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="P24" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q24" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="R24" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="S24" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="T24" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="U24" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="V24" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="W24" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="X24" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y24" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z24" s="17" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C25" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="D25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F25" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G25" s="17" t="n">
+        <v>341</v>
+      </c>
+      <c r="H25" s="17" t="n">
+        <v>647</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <v>362</v>
+      </c>
+      <c r="J25" s="17" t="n">
+        <v>686</v>
+      </c>
+      <c r="K25" s="17" t="n">
+        <v>507</v>
+      </c>
+      <c r="L25" s="17" t="n">
+        <v>889</v>
+      </c>
+      <c r="M25" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N25" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O25" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="P25" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q25" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="R25" s="17" t="n">
+        <v>79</v>
+      </c>
+      <c r="S25" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="U25" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="V25" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="W25" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="X25" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="Y25" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z25" s="17" t="n">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C26" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F26" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G26" s="17" t="n">
+        <v>392</v>
+      </c>
+      <c r="H26" s="17" t="n">
+        <v>743</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <v>413</v>
+      </c>
+      <c r="J26" s="17" t="n">
+        <v>782</v>
+      </c>
+      <c r="K26" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="L26" s="17" t="n">
+        <v>1009</v>
+      </c>
+      <c r="M26" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N26" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="P26" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q26" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="R26" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="S26" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="T26" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="U26" s="17" t="n">
+        <v>44</v>
+      </c>
+      <c r="V26" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="W26" s="17" t="n">
+        <v>57</v>
+      </c>
+      <c r="X26" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="Y26" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="Z26" s="17" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D27" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F27" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G27" s="17" t="n">
+        <v>442</v>
+      </c>
+      <c r="H27" s="17" t="n">
+        <v>839</v>
+      </c>
+      <c r="I27" s="17" t="n">
+        <v>463</v>
+      </c>
+      <c r="J27" s="17" t="n">
+        <v>878</v>
+      </c>
+      <c r="K27" s="17" t="n">
+        <v>633</v>
+      </c>
+      <c r="L27" s="17" t="n">
+        <v>1129</v>
+      </c>
+      <c r="M27" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N27" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O27" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="P27" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q27" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="R27" s="17" t="n">
+        <v>101</v>
+      </c>
+      <c r="S27" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T27" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="U27" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="V27" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="W27" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="X27" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="Y27" s="17" t="n">
+        <v>87</v>
+      </c>
+      <c r="Z27" s="17" t="n">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C28" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F28" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G28" s="17" t="n">
+        <v>493</v>
+      </c>
+      <c r="H28" s="17" t="n">
+        <v>935</v>
+      </c>
+      <c r="I28" s="17" t="n">
+        <v>514</v>
+      </c>
+      <c r="J28" s="17" t="n">
+        <v>974</v>
+      </c>
+      <c r="K28" s="17" t="n">
+        <v>696</v>
+      </c>
+      <c r="L28" s="17" t="n">
+        <v>1249</v>
+      </c>
+      <c r="M28" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N28" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O28" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="P28" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q28" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="R28" s="17" t="n">
+        <v>112</v>
+      </c>
+      <c r="S28" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="T28" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="U28" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="V28" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="W28" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="X28" s="17" t="n">
+        <v>88</v>
+      </c>
+      <c r="Y28" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="Z28" s="17" t="n">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D29" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F29" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G29" s="17" t="n">
+        <v>684</v>
+      </c>
+      <c r="H29" s="17" t="n">
+        <v>1298</v>
+      </c>
+      <c r="I29" s="17" t="n">
+        <v>705</v>
+      </c>
+      <c r="J29" s="17" t="n">
+        <v>1337</v>
+      </c>
+      <c r="K29" s="17" t="n">
+        <v>935</v>
+      </c>
+      <c r="L29" s="17" t="n">
+        <v>1703</v>
+      </c>
+      <c r="M29" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N29" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O29" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="P29" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q29" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="R29" s="17" t="n">
+        <v>151</v>
+      </c>
+      <c r="S29" s="17" t="n">
+        <v>49</v>
+      </c>
+      <c r="T29" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="U29" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="V29" s="17" t="n">
+        <v>86</v>
+      </c>
+      <c r="W29" s="17" t="n">
+        <v>97</v>
+      </c>
+      <c r="X29" s="17" t="n">
+        <v>121</v>
+      </c>
+      <c r="Y29" s="17" t="n">
+        <v>133</v>
+      </c>
+      <c r="Z29" s="17" t="n">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>785</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>1490</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>806</v>
+      </c>
+      <c r="J30" s="17" t="n">
+        <v>1529</v>
+      </c>
+      <c r="K30" s="17" t="n">
+        <v>1082</v>
+      </c>
+      <c r="L30" s="17" t="n">
+        <v>1942</v>
+      </c>
+      <c r="M30" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N30" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O30" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="P30" s="17" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q30" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="R30" s="17" t="n">
+        <v>181</v>
+      </c>
+      <c r="S30" s="17" t="n">
+        <v>56</v>
+      </c>
+      <c r="T30" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="U30" s="17" t="n">
+        <v>88</v>
+      </c>
+      <c r="V30" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="W30" s="17" t="n">
+        <v>113</v>
+      </c>
+      <c r="X30" s="17" t="n">
+        <v>138</v>
+      </c>
+      <c r="Y30" s="17" t="n">
+        <v>150</v>
+      </c>
+      <c r="Z30" s="17" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G31" s="17" t="n">
+        <v>884</v>
+      </c>
+      <c r="H31" s="17" t="n">
+        <v>1676</v>
+      </c>
+      <c r="I31" s="17" t="n">
+        <v>905</v>
+      </c>
+      <c r="J31" s="17" t="n">
+        <v>1715</v>
+      </c>
+      <c r="K31" s="17" t="n">
+        <v>1186</v>
+      </c>
+      <c r="L31" s="17" t="n">
+        <v>2176</v>
+      </c>
+      <c r="M31" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N31" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O31" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="P31" s="17" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q31" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="R31" s="17" t="n">
+        <v>196</v>
+      </c>
+      <c r="S31" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="T31" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="U31" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="V31" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="W31" s="17" t="n">
+        <v>126</v>
+      </c>
+      <c r="X31" s="17" t="n">
+        <v>155</v>
+      </c>
+      <c r="Y31" s="17" t="n">
+        <v>169</v>
+      </c>
+      <c r="Z31" s="17" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="G32" s="17" t="n">
+        <v>935</v>
+      </c>
+      <c r="H32" s="17" t="n">
+        <v>1774</v>
+      </c>
+      <c r="I32" s="17" t="n">
+        <v>956</v>
+      </c>
+      <c r="J32" s="17" t="n">
+        <v>1813</v>
+      </c>
+      <c r="K32" s="17" t="n">
+        <v>1249</v>
+      </c>
+      <c r="L32" s="17" t="n">
+        <v>2299</v>
+      </c>
+      <c r="M32" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N32" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O32" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="P32" s="17" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q32" s="17" t="n">
+        <v>66</v>
+      </c>
+      <c r="R32" s="17" t="n">
+        <v>207</v>
+      </c>
+      <c r="S32" s="17" t="n">
+        <v>66</v>
+      </c>
+      <c r="T32" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="U32" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="V32" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="W32" s="17" t="n">
+        <v>126</v>
+      </c>
+      <c r="X32" s="17" t="n">
+        <v>155</v>
+      </c>
+      <c r="Y32" s="17" t="n">
+        <v>169</v>
+      </c>
+      <c r="Z32" s="17" t="n">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F33" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G33" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H33" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="I33" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="J33" s="17" t="n">
+        <v>116</v>
+      </c>
+      <c r="K33" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="L33" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="M33" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N33" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O33" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="R33" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="S33" s="17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T33" s="17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="U33" s="17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V33" s="17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W33" s="17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X33" s="17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y33" s="17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Z33" s="17" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F34" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G34" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="H34" s="17" t="n">
+        <v>130</v>
+      </c>
+      <c r="I34" s="17" t="n">
+        <v>110</v>
+      </c>
+      <c r="J34" s="17" t="n">
+        <v>208</v>
+      </c>
+      <c r="K34" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="L34" s="17" t="n">
+        <v>223</v>
+      </c>
+      <c r="M34" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N34" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O34" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P34" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q34" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="R34" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="S34" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="T34" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="U34" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="V34" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="W34" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="X34" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y34" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z34" s="17" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C35" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D35" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F35" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G35" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="H35" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="I35" s="17" t="n">
+        <v>133</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <v>253</v>
+      </c>
+      <c r="K35" s="17" t="n">
+        <v>195</v>
+      </c>
+      <c r="L35" s="17" t="n">
+        <v>298</v>
+      </c>
+      <c r="M35" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N35" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O35" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="P35" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q35" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="R35" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="S35" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="T35" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="U35" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="V35" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="W35" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="X35" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="Y35" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z35" s="17" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C36" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D36" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F36" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G36" s="17" t="n">
+        <v>141</v>
+      </c>
+      <c r="H36" s="17" t="n">
+        <v>267</v>
+      </c>
+      <c r="I36" s="17" t="n">
+        <v>182</v>
+      </c>
+      <c r="J36" s="17" t="n">
+        <v>345</v>
+      </c>
+      <c r="K36" s="17" t="n">
+        <v>256</v>
+      </c>
+      <c r="L36" s="17" t="n">
+        <v>414</v>
+      </c>
+      <c r="M36" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N36" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O36" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="P36" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q36" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="R36" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="S36" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T36" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="U36" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="V36" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="W36" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="X36" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="Y36" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="Z36" s="17" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D37" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F37" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G37" s="17" t="n">
+        <v>191</v>
+      </c>
+      <c r="H37" s="17" t="n">
+        <v>363</v>
+      </c>
+      <c r="I37" s="17" t="n">
+        <v>232</v>
+      </c>
+      <c r="J37" s="17" t="n">
+        <v>441</v>
+      </c>
+      <c r="K37" s="17" t="n">
+        <v>330</v>
+      </c>
+      <c r="L37" s="17" t="n">
+        <v>534</v>
+      </c>
+      <c r="M37" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N37" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O37" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="P37" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q37" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="R37" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="S37" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T37" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="U37" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="V37" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="W37" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="X37" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="Y37" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="Z37" s="17" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G38" s="17" t="n">
+        <v>240</v>
+      </c>
+      <c r="H38" s="17" t="n">
+        <v>455</v>
+      </c>
+      <c r="I38" s="17" t="n">
+        <v>281</v>
+      </c>
+      <c r="J38" s="17" t="n">
+        <v>533</v>
+      </c>
+      <c r="K38" s="17" t="n">
+        <v>380</v>
+      </c>
+      <c r="L38" s="17" t="n">
+        <v>650</v>
+      </c>
+      <c r="M38" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O38" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P38" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q38" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="R38" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="S38" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="T38" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="U38" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="V38" s="17" t="n">
+        <v>36</v>
+      </c>
+      <c r="W38" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="X38" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="Y38" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="Z38" s="17" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G39" s="17" t="n">
+        <v>292</v>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>555</v>
+      </c>
+      <c r="I39" s="17" t="n">
+        <v>333</v>
+      </c>
+      <c r="J39" s="17" t="n">
+        <v>633</v>
+      </c>
+      <c r="K39" s="17" t="n">
+        <v>446</v>
+      </c>
+      <c r="L39" s="17" t="n">
+        <v>774</v>
+      </c>
+      <c r="M39" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N39" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O39" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="P39" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q39" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="R39" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="S39" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T39" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="U39" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="V39" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="W39" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="X39" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="Y39" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="Z39" s="17" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G40" s="17" t="n">
+        <v>341</v>
+      </c>
+      <c r="H40" s="17" t="n">
+        <v>647</v>
+      </c>
+      <c r="I40" s="17" t="n">
+        <v>382</v>
+      </c>
+      <c r="J40" s="17" t="n">
+        <v>725</v>
+      </c>
+      <c r="K40" s="17" t="n">
+        <v>507</v>
+      </c>
+      <c r="L40" s="17" t="n">
+        <v>889</v>
+      </c>
+      <c r="M40" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N40" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O40" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="P40" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q40" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="R40" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="S40" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="T40" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="U40" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="V40" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="W40" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="X40" s="17" t="n">
+        <v>67</v>
+      </c>
+      <c r="Y40" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="Z40" s="17" t="n">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C41" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D41" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F41" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G41" s="17" t="n">
+        <v>392</v>
+      </c>
+      <c r="H41" s="17" t="n">
+        <v>743</v>
+      </c>
+      <c r="I41" s="17" t="n">
+        <v>433</v>
+      </c>
+      <c r="J41" s="17" t="n">
+        <v>821</v>
+      </c>
+      <c r="K41" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="L41" s="17" t="n">
+        <v>1009</v>
+      </c>
+      <c r="M41" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N41" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O41" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="P41" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q41" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="R41" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="S41" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="T41" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="U41" s="17" t="n">
+        <v>48</v>
+      </c>
+      <c r="V41" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="W41" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="X41" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="Y41" s="17" t="n">
+        <v>83</v>
+      </c>
+      <c r="Z41" s="17" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G42" s="17" t="n">
+        <v>442</v>
+      </c>
+      <c r="H42" s="17" t="n">
+        <v>839</v>
+      </c>
+      <c r="I42" s="17" t="n">
+        <v>483</v>
+      </c>
+      <c r="J42" s="17" t="n">
+        <v>917</v>
+      </c>
+      <c r="K42" s="17" t="n">
+        <v>633</v>
+      </c>
+      <c r="L42" s="17" t="n">
+        <v>1129</v>
+      </c>
+      <c r="M42" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N42" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O42" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="P42" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q42" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="R42" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="S42" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="T42" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="U42" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="V42" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="W42" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="X42" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="Y42" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="Z42" s="17" t="n">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C43" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D43" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F43" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G43" s="17" t="n">
+        <v>493</v>
+      </c>
+      <c r="H43" s="17" t="n">
+        <v>935</v>
+      </c>
+      <c r="I43" s="17" t="n">
+        <v>534</v>
+      </c>
+      <c r="J43" s="17" t="n">
+        <v>1013</v>
+      </c>
+      <c r="K43" s="17" t="n">
+        <v>696</v>
+      </c>
+      <c r="L43" s="17" t="n">
+        <v>1249</v>
+      </c>
+      <c r="M43" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N43" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O43" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="P43" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q43" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="R43" s="17" t="n">
+        <v>118</v>
+      </c>
+      <c r="S43" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="T43" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="U43" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="V43" s="17" t="n">
+        <v>67</v>
+      </c>
+      <c r="W43" s="17" t="n">
+        <v>77</v>
+      </c>
+      <c r="X43" s="17" t="n">
+        <v>93</v>
+      </c>
+      <c r="Y43" s="17" t="n">
+        <v>102</v>
+      </c>
+      <c r="Z43" s="17" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B44" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D44" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G44" s="17" t="n">
+        <v>684</v>
+      </c>
+      <c r="H44" s="17" t="n">
+        <v>1298</v>
+      </c>
+      <c r="I44" s="17" t="n">
+        <v>725</v>
+      </c>
+      <c r="J44" s="17" t="n">
+        <v>1376</v>
+      </c>
+      <c r="K44" s="17" t="n">
+        <v>935</v>
+      </c>
+      <c r="L44" s="17" t="n">
+        <v>1703</v>
+      </c>
+      <c r="M44" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N44" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O44" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="P44" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q44" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="R44" s="17" t="n">
+        <v>157</v>
+      </c>
+      <c r="S44" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="T44" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="U44" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="V44" s="17" t="n">
+        <v>91</v>
+      </c>
+      <c r="W44" s="17" t="n">
+        <v>102</v>
+      </c>
+      <c r="X44" s="17" t="n">
+        <v>126</v>
+      </c>
+      <c r="Y44" s="17" t="n">
+        <v>139</v>
+      </c>
+      <c r="Z44" s="17" t="n">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G45" s="17" t="n">
+        <v>785</v>
+      </c>
+      <c r="H45" s="17" t="n">
+        <v>1490</v>
+      </c>
+      <c r="I45" s="17" t="n">
+        <v>826</v>
+      </c>
+      <c r="J45" s="17" t="n">
+        <v>1568</v>
+      </c>
+      <c r="K45" s="17" t="n">
+        <v>1082</v>
+      </c>
+      <c r="L45" s="17" t="n">
+        <v>1942</v>
+      </c>
+      <c r="M45" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N45" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O45" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="P45" s="17" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q45" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="R45" s="17" t="n">
+        <v>187</v>
+      </c>
+      <c r="S45" s="17" t="n">
+        <v>59</v>
+      </c>
+      <c r="T45" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="U45" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="V45" s="17" t="n">
+        <v>103</v>
+      </c>
+      <c r="W45" s="17" t="n">
+        <v>118</v>
+      </c>
+      <c r="X45" s="17" t="n">
+        <v>143</v>
+      </c>
+      <c r="Y45" s="17" t="n">
+        <v>156</v>
+      </c>
+      <c r="Z45" s="17" t="n">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C46" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D46" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F46" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G46" s="17" t="n">
+        <v>884</v>
+      </c>
+      <c r="H46" s="17" t="n">
+        <v>1676</v>
+      </c>
+      <c r="I46" s="17" t="n">
+        <v>925</v>
+      </c>
+      <c r="J46" s="17" t="n">
+        <v>1754</v>
+      </c>
+      <c r="K46" s="17" t="n">
+        <v>1186</v>
+      </c>
+      <c r="L46" s="17" t="n">
+        <v>2176</v>
+      </c>
+      <c r="M46" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N46" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O46" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="P46" s="17" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q46" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="R46" s="17" t="n">
+        <v>202</v>
+      </c>
+      <c r="S46" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="T46" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="U46" s="17" t="n">
+        <v>103</v>
+      </c>
+      <c r="V46" s="17" t="n">
+        <v>115</v>
+      </c>
+      <c r="W46" s="17" t="n">
+        <v>131</v>
+      </c>
+      <c r="X46" s="17" t="n">
+        <v>160</v>
+      </c>
+      <c r="Y46" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="Z46" s="17" t="n">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="F47" s="17" t="n">
+        <v>78</v>
+      </c>
+      <c r="G47" s="17" t="n">
+        <v>935</v>
+      </c>
+      <c r="H47" s="17" t="n">
+        <v>1774</v>
+      </c>
+      <c r="I47" s="17" t="n">
+        <v>976</v>
+      </c>
+      <c r="J47" s="17" t="n">
+        <v>1852</v>
+      </c>
+      <c r="K47" s="17" t="n">
+        <v>1249</v>
+      </c>
+      <c r="L47" s="17" t="n">
+        <v>2299</v>
+      </c>
+      <c r="M47" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="N47" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="O47" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="P47" s="17" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q47" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="R47" s="17" t="n">
+        <v>213</v>
+      </c>
+      <c r="S47" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="T47" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="U47" s="17" t="n">
+        <v>103</v>
+      </c>
+      <c r="V47" s="17" t="n">
+        <v>115</v>
+      </c>
+      <c r="W47" s="17" t="n">
+        <v>131</v>
+      </c>
+      <c r="X47" s="17" t="n">
+        <v>160</v>
+      </c>
+      <c r="Y47" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="Z47" s="17" t="n">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C48" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F48" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G48" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="H48" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="I48" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="J48" s="17" t="n">
+        <v>155</v>
+      </c>
+      <c r="K48" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="L48" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="M48" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N48" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P48" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q48" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="R48" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="S48" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T48" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="V48" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="W48" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="X48" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z48" s="17" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C49" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D49" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F49" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G49" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="H49" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="I49" s="17" t="n">
+        <v>105</v>
+      </c>
+      <c r="J49" s="17" t="n">
+        <v>199</v>
+      </c>
+      <c r="K49" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="L49" s="17" t="n">
+        <v>141</v>
+      </c>
+      <c r="M49" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N49" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O49" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="P49" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q49" s="17" t="n">
+        <v>11</v>
+      </c>
+      <c r="R49" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="S49" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="T49" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="U49" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="V49" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="W49" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="X49" s="17" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y49" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z49" s="17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B50" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C50" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="D50" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F50" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G50" s="17" t="n">
+        <v>92</v>
+      </c>
+      <c r="H50" s="17" t="n">
+        <v>175</v>
+      </c>
+      <c r="I50" s="17" t="n">
+        <v>154</v>
+      </c>
+      <c r="J50" s="17" t="n">
+        <v>292</v>
+      </c>
+      <c r="K50" s="17" t="n">
+        <v>195</v>
+      </c>
+      <c r="L50" s="17" t="n">
+        <v>298</v>
+      </c>
+      <c r="M50" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N50" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O50" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="P50" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="R50" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="S50" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="T50" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="U50" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="V50" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="W50" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="X50" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y50" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z50" s="17" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C51" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="D51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F51" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G51" s="17" t="n">
+        <v>141</v>
+      </c>
+      <c r="H51" s="17" t="n">
+        <v>267</v>
+      </c>
+      <c r="I51" s="17" t="n">
+        <v>203</v>
+      </c>
+      <c r="J51" s="17" t="n">
+        <v>384</v>
+      </c>
+      <c r="K51" s="17" t="n">
+        <v>256</v>
+      </c>
+      <c r="L51" s="17" t="n">
+        <v>414</v>
+      </c>
+      <c r="M51" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N51" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O51" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="P51" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q51" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="R51" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="S51" s="17" t="n">
+        <v>18</v>
+      </c>
+      <c r="T51" s="17" t="n">
+        <v>19</v>
+      </c>
+      <c r="U51" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="V51" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="W51" s="17" t="n">
+        <v>32</v>
+      </c>
+      <c r="X51" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y51" s="17" t="n">
+        <v>43</v>
+      </c>
+      <c r="Z51" s="17" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C52" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="D52" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F52" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G52" s="17" t="n">
+        <v>191</v>
+      </c>
+      <c r="H52" s="17" t="n">
+        <v>363</v>
+      </c>
+      <c r="I52" s="17" t="n">
+        <v>253</v>
+      </c>
+      <c r="J52" s="17" t="n">
+        <v>480</v>
+      </c>
+      <c r="K52" s="17" t="n">
+        <v>330</v>
+      </c>
+      <c r="L52" s="17" t="n">
+        <v>534</v>
+      </c>
+      <c r="M52" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N52" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O52" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="P52" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="Q52" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="R52" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="S52" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="T52" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="U52" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="V52" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="W52" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="X52" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="Y52" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="Z52" s="17" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B53" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C53" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="D53" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F53" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G53" s="17" t="n">
+        <v>240</v>
+      </c>
+      <c r="H53" s="17" t="n">
+        <v>455</v>
+      </c>
+      <c r="I53" s="17" t="n">
+        <v>302</v>
+      </c>
+      <c r="J53" s="17" t="n">
+        <v>572</v>
+      </c>
+      <c r="K53" s="17" t="n">
+        <v>380</v>
+      </c>
+      <c r="L53" s="17" t="n">
+        <v>650</v>
+      </c>
+      <c r="M53" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N53" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O53" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P53" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="Q53" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="R53" s="17" t="n">
+        <v>69</v>
+      </c>
+      <c r="S53" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="U53" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="V53" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="W53" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="X53" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y53" s="17" t="n">
+        <v>61</v>
+      </c>
+      <c r="Z53" s="17" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C54" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D54" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F54" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G54" s="17" t="n">
+        <v>292</v>
+      </c>
+      <c r="H54" s="17" t="n">
+        <v>555</v>
+      </c>
+      <c r="I54" s="17" t="n">
+        <v>354</v>
+      </c>
+      <c r="J54" s="17" t="n">
+        <v>672</v>
+      </c>
+      <c r="K54" s="17" t="n">
+        <v>446</v>
+      </c>
+      <c r="L54" s="17" t="n">
+        <v>774</v>
+      </c>
+      <c r="M54" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N54" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O54" s="17" t="n">
+        <v>20</v>
+      </c>
+      <c r="P54" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q54" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="R54" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="S54" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="T54" s="17" t="n">
+        <v>33</v>
+      </c>
+      <c r="U54" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="V54" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="W54" s="17" t="n">
+        <v>53</v>
+      </c>
+      <c r="X54" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="Y54" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="Z54" s="17" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B55" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C55" s="17" t="n">
+        <v>70</v>
+      </c>
+      <c r="D55" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G55" s="17" t="n">
+        <v>341</v>
+      </c>
+      <c r="H55" s="17" t="n">
+        <v>647</v>
+      </c>
+      <c r="I55" s="17" t="n">
+        <v>403</v>
+      </c>
+      <c r="J55" s="17" t="n">
+        <v>764</v>
+      </c>
+      <c r="K55" s="17" t="n">
+        <v>507</v>
+      </c>
+      <c r="L55" s="17" t="n">
+        <v>889</v>
+      </c>
+      <c r="M55" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N55" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O55" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="P55" s="17" t="n">
+        <v>74</v>
+      </c>
+      <c r="Q55" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="R55" s="17" t="n">
+        <v>91</v>
+      </c>
+      <c r="S55" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="T55" s="17" t="n">
+        <v>37</v>
+      </c>
+      <c r="U55" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="V55" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="W55" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="X55" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="Y55" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z55" s="17" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C56" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="D56" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G56" s="17" t="n">
+        <v>392</v>
+      </c>
+      <c r="H56" s="17" t="n">
+        <v>743</v>
+      </c>
+      <c r="I56" s="17" t="n">
+        <v>454</v>
+      </c>
+      <c r="J56" s="17" t="n">
+        <v>860</v>
+      </c>
+      <c r="K56" s="17" t="n">
+        <v>570</v>
+      </c>
+      <c r="L56" s="17" t="n">
+        <v>1009</v>
+      </c>
+      <c r="M56" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N56" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O56" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="P56" s="17" t="n">
+        <v>85</v>
+      </c>
+      <c r="Q56" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="R56" s="17" t="n">
+        <v>102</v>
+      </c>
+      <c r="S56" s="17" t="n">
+        <v>35</v>
+      </c>
+      <c r="T56" s="17" t="n">
+        <v>41</v>
+      </c>
+      <c r="U56" s="17" t="n">
+        <v>52</v>
+      </c>
+      <c r="V56" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="W56" s="17" t="n">
+        <v>67</v>
+      </c>
+      <c r="X56" s="17" t="n">
+        <v>81</v>
+      </c>
+      <c r="Y56" s="17" t="n">
+        <v>89</v>
+      </c>
+      <c r="Z56" s="17" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B57" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C57" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="D57" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F57" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G57" s="17" t="n">
+        <v>442</v>
+      </c>
+      <c r="H57" s="17" t="n">
+        <v>839</v>
+      </c>
+      <c r="I57" s="17" t="n">
+        <v>504</v>
+      </c>
+      <c r="J57" s="17" t="n">
+        <v>956</v>
+      </c>
+      <c r="K57" s="17" t="n">
+        <v>633</v>
+      </c>
+      <c r="L57" s="17" t="n">
+        <v>1129</v>
+      </c>
+      <c r="M57" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N57" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O57" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="P57" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="Q57" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="R57" s="17" t="n">
+        <v>113</v>
+      </c>
+      <c r="S57" s="17" t="n">
+        <v>38</v>
+      </c>
+      <c r="T57" s="17" t="n">
+        <v>46</v>
+      </c>
+      <c r="U57" s="17" t="n">
+        <v>58</v>
+      </c>
+      <c r="V57" s="17" t="n">
+        <v>65</v>
+      </c>
+      <c r="W57" s="17" t="n">
+        <v>75</v>
+      </c>
+      <c r="X57" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y57" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="Z57" s="17" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C58" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D58" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F58" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G58" s="17" t="n">
+        <v>493</v>
+      </c>
+      <c r="H58" s="17" t="n">
+        <v>935</v>
+      </c>
+      <c r="I58" s="17" t="n">
+        <v>555</v>
+      </c>
+      <c r="J58" s="17" t="n">
+        <v>1052</v>
+      </c>
+      <c r="K58" s="17" t="n">
+        <v>696</v>
+      </c>
+      <c r="L58" s="17" t="n">
+        <v>1249</v>
+      </c>
+      <c r="M58" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N58" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O58" s="17" t="n">
+        <v>34</v>
+      </c>
+      <c r="P58" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="Q58" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="R58" s="17" t="n">
+        <v>124</v>
+      </c>
+      <c r="S58" s="17" t="n">
+        <v>42</v>
+      </c>
+      <c r="T58" s="17" t="n">
+        <v>50</v>
+      </c>
+      <c r="U58" s="17" t="n">
+        <v>63</v>
+      </c>
+      <c r="V58" s="17" t="n">
+        <v>71</v>
+      </c>
+      <c r="W58" s="17" t="n">
+        <v>82</v>
+      </c>
+      <c r="X58" s="17" t="n">
+        <v>98</v>
+      </c>
+      <c r="Y58" s="17" t="n">
+        <v>108</v>
+      </c>
+      <c r="Z58" s="17" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C59" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D59" s="17" t="n">
+        <v>40</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F59" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G59" s="17" t="n">
+        <v>684</v>
+      </c>
+      <c r="H59" s="17" t="n">
+        <v>1298</v>
+      </c>
+      <c r="I59" s="17" t="n">
+        <v>746</v>
+      </c>
+      <c r="J59" s="17" t="n">
+        <v>1415</v>
+      </c>
+      <c r="K59" s="17" t="n">
+        <v>935</v>
+      </c>
+      <c r="L59" s="17" t="n">
+        <v>1703</v>
+      </c>
+      <c r="M59" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N59" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O59" s="17" t="n">
+        <v>47</v>
+      </c>
+      <c r="P59" s="17" t="n">
+        <v>146</v>
+      </c>
+      <c r="Q59" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="R59" s="17" t="n">
+        <v>163</v>
+      </c>
+      <c r="S59" s="17" t="n">
+        <v>55</v>
+      </c>
+      <c r="T59" s="17" t="n">
+        <v>67</v>
+      </c>
+      <c r="U59" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="V59" s="17" t="n">
+        <v>95</v>
+      </c>
+      <c r="W59" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="X59" s="17" t="n">
+        <v>131</v>
+      </c>
+      <c r="Y59" s="17" t="n">
+        <v>145</v>
+      </c>
+      <c r="Z59" s="17" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C60" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D60" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F60" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G60" s="17" t="n">
+        <v>785</v>
+      </c>
+      <c r="H60" s="17" t="n">
+        <v>1490</v>
+      </c>
+      <c r="I60" s="17" t="n">
+        <v>847</v>
+      </c>
+      <c r="J60" s="17" t="n">
+        <v>1607</v>
+      </c>
+      <c r="K60" s="17" t="n">
+        <v>1082</v>
+      </c>
+      <c r="L60" s="17" t="n">
+        <v>1942</v>
+      </c>
+      <c r="M60" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N60" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O60" s="17" t="n">
+        <v>54</v>
+      </c>
+      <c r="P60" s="17" t="n">
+        <v>176</v>
+      </c>
+      <c r="Q60" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="R60" s="17" t="n">
+        <v>193</v>
+      </c>
+      <c r="S60" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="T60" s="17" t="n">
+        <v>76</v>
+      </c>
+      <c r="U60" s="17" t="n">
+        <v>96</v>
+      </c>
+      <c r="V60" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="W60" s="17" t="n">
+        <v>123</v>
+      </c>
+      <c r="X60" s="17" t="n">
+        <v>148</v>
+      </c>
+      <c r="Y60" s="17" t="n">
+        <v>162</v>
+      </c>
+      <c r="Z60" s="17" t="n">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C61" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D61" s="17" t="n">
+        <v>80</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F61" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G61" s="17" t="n">
+        <v>884</v>
+      </c>
+      <c r="H61" s="17" t="n">
+        <v>1676</v>
+      </c>
+      <c r="I61" s="17" t="n">
+        <v>946</v>
+      </c>
+      <c r="J61" s="17" t="n">
+        <v>1793</v>
+      </c>
+      <c r="K61" s="17" t="n">
+        <v>1186</v>
+      </c>
+      <c r="L61" s="17" t="n">
+        <v>2176</v>
+      </c>
+      <c r="M61" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N61" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O61" s="17" t="n">
+        <v>60</v>
+      </c>
+      <c r="P61" s="17" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q61" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="R61" s="17" t="n">
+        <v>208</v>
+      </c>
+      <c r="S61" s="17" t="n">
+        <v>68</v>
+      </c>
+      <c r="T61" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="U61" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="V61" s="17" t="n">
+        <v>119</v>
+      </c>
+      <c r="W61" s="17" t="n">
+        <v>136</v>
+      </c>
+      <c r="X61" s="17" t="n">
+        <v>165</v>
+      </c>
+      <c r="Y61" s="17" t="n">
+        <v>181</v>
+      </c>
+      <c r="Z61" s="17" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="inlineStr">
+        <is>
+          <t>MIMO</t>
+        </is>
+      </c>
+      <c r="B62" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C62" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="D62" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="E62" s="17" t="n">
+        <v>62</v>
+      </c>
+      <c r="F62" s="17" t="n">
+        <v>117</v>
+      </c>
+      <c r="G62" s="17" t="n">
+        <v>935</v>
+      </c>
+      <c r="H62" s="17" t="n">
+        <v>1774</v>
+      </c>
+      <c r="I62" s="17" t="n">
+        <v>997</v>
+      </c>
+      <c r="J62" s="17" t="n">
+        <v>1891</v>
+      </c>
+      <c r="K62" s="17" t="n">
+        <v>1249</v>
+      </c>
+      <c r="L62" s="17" t="n">
+        <v>2299</v>
+      </c>
+      <c r="M62" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="N62" s="17" t="n">
+        <v>17</v>
+      </c>
+      <c r="O62" s="17" t="n">
+        <v>64</v>
+      </c>
+      <c r="P62" s="17" t="n">
+        <v>202</v>
+      </c>
+      <c r="Q62" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="R62" s="17" t="n">
+        <v>219</v>
+      </c>
+      <c r="S62" s="17" t="n">
+        <v>72</v>
+      </c>
+      <c r="T62" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="U62" s="17" t="n">
+        <v>107</v>
+      </c>
+      <c r="V62" s="17" t="n">
+        <v>119</v>
+      </c>
+      <c r="W62" s="17" t="n">
+        <v>136</v>
+      </c>
+      <c r="X62" s="17" t="n">
+        <v>165</v>
+      </c>
+      <c r="Y62" s="17" t="n">
+        <v>181</v>
+      </c>
+      <c r="Z62" s="17" t="n">
+        <v>220</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
